--- a/XXXXXXX_GUIA.xlsx
+++ b/XXXXXXX_GUIA.xlsx
@@ -1915,7 +1915,7 @@
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="84" t="inlineStr">
         <is>
-          <t>Cargo:  DIRECTOR DE CUENTAS MEDICAS</t>
+          <t>Cargo: GERENTE DE CUENTAS MEDICAS</t>
         </is>
       </c>
       <c r="I25" s="84" t="n"/>
